--- a/etc/hebrew/verbs.xlsx
+++ b/etc/hebrew/verbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1539,6 +1539,369 @@
       </c>
       <c r="G33" s="2" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>succeed</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>לְהַצְלִיחַ</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>מַצְלִיחַ</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>מַצְלִיחָה</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>מַצְלִיחִים</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>מַצְלִיחוֹת</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>believe</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>לְהַאֲמִין</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>מַאֲמִין</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>מַאֲמִינָה</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>מַאֲמִינִים</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>מַאֲמִינוֹת</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>sit</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>לָשֶׁבֶת</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>יוֹשֵׁב</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>יוֹשֶׁבֶת</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>יוֹשְׁבִים</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>יוֹשְׁבוֹת</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>see; watch</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>לִרְאוֹת</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>רוֹאֶה</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>רוֹאָה</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>רוֹאִים</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>רוֹאוֹת</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>play</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>לְשַׂחֵק</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׂחֵק</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׂחֶקֶת</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׂחֲקִים</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׂחֲקוֹת</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>teach</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>לְלַמֵּד</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>מְלַמֵּד</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>מְלַמֶּדֶת</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>מְלַמְּדִים</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>מְלַמְּדוֹת</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>dance</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>לִרְקוֹד</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>רוֹקֵד</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>רוֹקֶדֶת</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>רוֹקְדִים</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>רוֹקְדוֹת</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>feel</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>לְהַרְגִּישׁ</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>מַרְגִּישׁ</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>מַרְגִּישָׁה</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>מַרְגִּישִׁים</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>מַרְגִּישׁוֹת</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>begin</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>לְהַתְחִיל</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>מַתְחִיל</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>מַתְחִילָה</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>מַתְחִילִים</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>מַתְחִילוֹת</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>לִשְׁאוֹל</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹאֵל</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹאֶלֶת</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹאֲלִים</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹאֲלוֹת</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>walk around; travel</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>לְטַיֵּל</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>מְטַיֵּל</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>מְטַיֶּלֶת</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>מְטַיְּלִים</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>מְטַיְּלוֹת</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/verbs.xlsx
+++ b/etc/hebrew/verbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1902,6 +1902,635 @@
       </c>
       <c r="G44" s="2" t="n"/>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>want</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>לִרְצוֹת</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>רוֹצֶה</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>רוֹצָה</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>רוֹצִים</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>רוֹצוֹת</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>tell; tell a story</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>לְסַפֵּר</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>מְסַפֵּר</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>מְסַפֶּרֶת</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>מְסַפְּרִים</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>מְסַפְּרוֹת</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>decide</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>לְהַחְלִיט</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>מַחְלִיט</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>מַחְלִיטָה</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>מַחְלִיטִים</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>מַחְלִיטוֹת</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>go out; leave</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>לָצֵאת</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>יוֹצֵא</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>יוֹצֵאת</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>יוֹצְאִים</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>יוֹצְאוֹת</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>invite</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>לְהַזְמִין</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>מַזְמִין</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>מַזְמִינָה</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>מַזְמִינִים</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>מַזְמִינוֹת</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>take</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>לָקַחַת</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>לוֹקֵחַ</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>לוֹקַחַת</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>לוֹקְחִים</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>לוֹקְחוֹת</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>arrive</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>לְהַגִּיעַ</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>מַגִּיעַ</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>מַגִּיעָה</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>מַגִּיעִים</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>מַגִּיעוֹת</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>give</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>לָתֵת</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>נוֹתֵן</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>נוֹתֶנֶת</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>נוֹתְנִים</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>נוֹתְנוֹת</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>receive; get</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>לְקַבֵּל</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>מְקַבֵּל</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>מְקַבֶּלֶת</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>מְקַבְּלִים</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>מְקַבְּלוֹת</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>pay</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>לְשַׁלֵּם</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׁלֵּם</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׁלֶּמֶת</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׁלְּמִים</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>מְשַׁלְּמוֹת</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>send</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>לִשְׁלוֹחַ</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹלֵחַ</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹלַחַת</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹלְחִים</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>שׁוֹלְחוֹת</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>לַעֲנוֹת</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>עוֹנֶה</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>עוֹנָה</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>עוֹנִים</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>עוֹנוֹת</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>sleep</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>לִישׁוֹן</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>יָשֵׁן</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>יְשֵׁנָה</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>יְשֵׁנִים</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>יְשֵׁנוֹת</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>descend; get off</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>לָרֶדֶת</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>יוֹרֵד</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>יוֹרֶדֶת</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>יוֹרְדִים</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>יוֹרְדוֹת</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>remember</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>לִזְכֹּר</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>זוֹכֵר</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>זוֹכֶרֶת</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>זוֹכְרִים</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>זוֹכְרוֹת</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>stand</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>לַעֲמֹד</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>עוֹמֵד</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>עוֹמֶדֶת</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>עוֹמְדִים</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>עוֹמְדוֹת</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>light; turn on</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>לְהַדְלִיק</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>מַדְלִיק</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>מַדְלִיקָה</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>מַדְלִיקִים</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>מַדְלִיקוֹת</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/verbs.xlsx
+++ b/etc/hebrew/verbs.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2531,6 +2531,228 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>dream (verb)</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>לַחֲלוֹם</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>חוֹלֵם</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>חוֹלֶמֶת</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>חוֹלְמִים</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>חוֹלְמוֹת</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>put on shoes</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>לִנְעֹל</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>נוֹעֵל</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>נוֹעֶלֶת</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>נוֹעֲלִים</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>נוֹעֲלוֹת</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>put on a hat; bandage</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>לַחֲבֹשׁ</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>חוֹבֵשׁ</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>חוֹבֶשֶׁת</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>חוֹבְשִׁים</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>חוֹבְשׁוֹת</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>enter</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>לְהִכָּנֵס</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>נִכְנָס</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>נִכְנֶסֶת</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>נִכְנָסִים</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>נִכְנָסוֹת</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>smoke (verb)</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>לְעַשֵּׁן</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>מְעַשֵּׁן</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>מְעַשֶּׁנֶת</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>מְעַשְּׁנִים</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>מְעַשְּׁנוֹת</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>לַעֲצֹר</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>עוֹצֵר</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>עוֹצֶרֶת</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>עוֹצְרִים</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>עוֹצְרוֹת</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>verb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
